--- a/Tableau de synthèse Thibault Merland.xlsx
+++ b/Tableau de synthèse Thibault Merland.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Merla\Bureau\Portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03A89759-FB57-4BF5-8F0A-F57137B485BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7233680-8EFD-49FE-97C1-4A711AC8384B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -159,7 +159,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-1]_-;\-* #,##0.00\ [$€-1]_-;_-* &quot;-&quot;??\ [$€-1]_-"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -227,6 +227,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -627,7 +633,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -692,9 +698,51 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -719,47 +767,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1080,54 +1092,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22" t="s">
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="22"/>
+      <c r="H1" s="25"/>
     </row>
     <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
     </row>
     <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="23"/>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="29" t="s">
+      <c r="A3" s="37"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="24"/>
-      <c r="H3" s="30"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="44"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="28"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="42"/>
       <c r="F4" s="12" t="s">
         <v>5</v>
       </c>
@@ -1139,22 +1151,22 @@
       </c>
     </row>
     <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="43"/>
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="36"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="31" t="s">
+      <c r="A6" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="39" t="s">
+      <c r="B6" s="32" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1177,8 +1189,8 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="324.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="32"/>
-      <c r="B7" s="40"/>
+      <c r="A7" s="24"/>
+      <c r="B7" s="33"/>
       <c r="C7" s="20" t="s">
         <v>17</v>
       </c>
@@ -1234,16 +1246,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.35">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="34"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="34"/>
-      <c r="G8" s="34"/>
-      <c r="H8" s="35"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+      <c r="H8" s="28"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1733,16 +1745,16 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.35">
-      <c r="A19" s="36" t="s">
+      <c r="A19" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="37"/>
-      <c r="C19" s="37"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="37"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="37"/>
-      <c r="H19" s="38"/>
+      <c r="B19" s="30"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="30"/>
+      <c r="H19" s="31"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1784,7 +1796,7 @@
         <v>27</v>
       </c>
       <c r="B20" s="8"/>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="46" t="s">
         <v>24</v>
       </c>
       <c r="D20" s="15"/>
@@ -1836,7 +1848,7 @@
       <c r="C21" s="15"/>
       <c r="D21" s="15"/>
       <c r="E21" s="15"/>
-      <c r="F21" s="15" t="s">
+      <c r="F21" s="45" t="s">
         <v>24</v>
       </c>
       <c r="G21" s="15"/>
@@ -1883,7 +1895,7 @@
       </c>
       <c r="B22" s="8"/>
       <c r="C22" s="15"/>
-      <c r="D22" s="15" t="s">
+      <c r="D22" s="45" t="s">
         <v>24</v>
       </c>
       <c r="E22" s="15"/>
@@ -1927,12 +1939,12 @@
       <c r="AQ22"/>
     </row>
     <row r="23" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="44" t="s">
+      <c r="A23" s="22" t="s">
         <v>30</v>
       </c>
       <c r="B23" s="8"/>
       <c r="C23" s="15"/>
-      <c r="D23" s="15" t="s">
+      <c r="D23" s="45" t="s">
         <v>24</v>
       </c>
       <c r="E23" s="15"/>
@@ -1981,10 +1993,9 @@
       </c>
       <c r="B24" s="8"/>
       <c r="C24" s="15"/>
-      <c r="D24" s="15" t="s">
+      <c r="E24" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="E24" s="15"/>
       <c r="F24" s="15"/>
       <c r="G24" s="15"/>
       <c r="H24" s="16"/>
@@ -2115,16 +2126,16 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.35">
-      <c r="A27" s="36" t="s">
+      <c r="A27" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="37"/>
-      <c r="C27" s="37"/>
-      <c r="D27" s="37"/>
-      <c r="E27" s="37"/>
-      <c r="F27" s="37"/>
-      <c r="G27" s="37"/>
-      <c r="H27" s="38"/>
+      <c r="B27" s="30"/>
+      <c r="C27" s="30"/>
+      <c r="D27" s="30"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="30"/>
+      <c r="G27" s="30"/>
+      <c r="H27" s="31"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2569,6 +2580,11 @@
     <row r="81" customFormat="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2576,11 +2592,6 @@
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -2600,6 +2611,14 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="264d44c6-c287-4ecc-a3ad-3b5fb639d43d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D84CA41CAB2F2D4C878084587D8423E5" ma:contentTypeVersion="11" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="363139b195f1e8a40f47b975ac3ad6a3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="264d44c6-c287-4ecc-a3ad-3b5fb639d43d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="10ccbda18575f6737e4b05b337dc6176" ns3:_="">
     <xsd:import namespace="264d44c6-c287-4ecc-a3ad-3b5fb639d43d"/>
@@ -2787,14 +2806,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="264d44c6-c287-4ecc-a3ad-3b5fb639d43d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B017DC1C-DD72-4F98-898D-9D6E1CB4C1E1}">
   <ds:schemaRefs>
@@ -2804,6 +2815,22 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C8E0CF9-4DA9-461A-9D42-7F5EDB84B399}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="264d44c6-c287-4ecc-a3ad-3b5fb639d43d"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AA897D9-2ED2-43CA-BF69-9438382B4C97}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2819,20 +2846,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C8E0CF9-4DA9-461A-9D42-7F5EDB84B399}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="264d44c6-c287-4ecc-a3ad-3b5fb639d43d"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>